--- a/examples/09-extensions.xlsx
+++ b/examples/09-extensions.xlsx
@@ -13,6 +13,28 @@
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -464,7 +486,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -518,6 +540,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Sorted</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -546,6 +578,15 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="J2" cm="1">
+        <f t="array" ref="J2:J5">_xlfn._xlws.SORT(A2:A5)</f>
+        <v/>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0042</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -574,6 +615,11 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>North</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -602,6 +648,11 @@
           <t>Open</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>South</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -628,6 +679,11 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>Open</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>West</t>
         </is>
       </c>
     </row>
@@ -647,6 +703,9 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <ignoredErrors>
+    <ignoredError sqref="K2" numberStoredAsText="1"/>
+  </ignoredErrors>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">

--- a/examples/09-extensions.xlsx
+++ b/examples/09-extensions.xlsx
@@ -163,6 +163,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>tc={6D3A9E4C-2F5B-4C7D-9E8F-0A1B2C3D4E5F}</author>
+    <author>tc={8F5C1A6E-4B7D-4E9F-9A0B-2C3D4E5F6071}</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
@@ -173,6 +174,13 @@
     Is Q4 final?
 Reply:
     Yes, checked twice.</t>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="1" shapeId="0">
+      <text>
+        <t>[Threaded comment]
+Comment:
+    @Olena Koval East grew again, please check Q4</t>
       </text>
     </comment>
   </commentList>
@@ -477,6 +485,12 @@
   <threadedComment ref="A3" id="{7E4B0F5D-3A6C-4D8E-8F9A-1B2C3D4E5F60}" parentId="{6D3A9E4C-2F5B-4C7D-9E8F-0A1B2C3D4E5F}" personId="{5C2F8D3B-1E4A-4B6C-8D7E-9F0A1B2C3D4E}" dT="2026-01-02T09:30:00.00">
     <text>Yes, checked twice.</text>
   </threadedComment>
+  <threadedComment ref="E4" id="{8F5C1A6E-4B7D-4E9F-9A0B-2C3D4E5F6071}" personId="{5C2F8D3B-1E4A-4B6C-8D7E-9F0A1B2C3D4E}" dT="2026-01-03T11:00:00.00" done="1">
+    <text>@Olena Koval East grew again, please check Q4</text>
+    <mentions xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments">
+      <mention mentionpersonId="{4B1E7C2A-0D3F-4A5B-9C6D-7E8F9A0B1C2D}" mentionId="{9A6D2B7F-5C8E-4FA0-8B1C-3D4E5F607182}" startIndex="0" length="12"/>
+    </mentions>
+  </threadedComment>
 </ThreadedComments>
 </file>
 
@@ -486,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -684,6 +698,20 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>West</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Change (columns)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Change (win/loss)</t>
         </is>
       </c>
     </row>
@@ -720,6 +748,25 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>F2:F5</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="iconSet" priority="2" id="{9F0C2E1A-5B7D-4C3E-8A21-6D4F0B9E7C16}">
+            <x14:iconSet iconSet="3Stars" custom="1">
+              <x14:cfvo type="percent">
+                <xm:f>0</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>33</xm:f>
+              </x14:cfvo>
+              <x14:cfvo type="percent">
+                <xm:f>67</xm:f>
+              </x14:cfvo>
+              <x14:cfIcon iconSet="3Flags" iconId="0"/>
+              <x14:cfIcon iconSet="NoIcons" iconId="0"/>
+              <x14:cfIcon iconSet="3Stars" iconId="2"/>
+            </x14:iconSet>
+          </x14:cfRule>
+          <xm:sqref>E2:E5</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -763,6 +810,38 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
+        <x14:sparklineGroup type="column" negative="1" high="1" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sales!F2:F5</xm:f>
+              <xm:sqref>F7</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
+        <x14:sparklineGroup type="stacked" negative="1" displayEmptyCellsAs="gap">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Sales!F2:F5</xm:f>
+              <xm:sqref>F8</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
       </x14:sparklineGroups>
     </ext>
   </extLst>
